--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -539,7 +539,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -548,10 +548,10 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>71.79000000000001</v>
+        <v>71.05</v>
       </c>
       <c r="H3">
         <v>5.8</v>
@@ -565,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -574,10 +574,10 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>82.5</v>
+        <v>82.05</v>
       </c>
       <c r="H4">
         <v>6.5</v>
@@ -617,10 +617,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -629,7 +629,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="H6">
         <v>5.6</v>
@@ -705,13 +705,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -728,13 +728,13 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -862,7 +862,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -871,10 +871,10 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>71.79000000000001</v>
+        <v>71.05</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -888,7 +888,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -897,10 +897,10 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>82.5</v>
+        <v>82.05</v>
       </c>
       <c r="H4">
         <v>6.5</v>
@@ -940,10 +940,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="H6">
         <v>5.7</v>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,51 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DEL VALLE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -91,21 +133,87 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>BUSTOS</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>FERRER</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
     <t>VANESA</t>
   </si>
   <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>ALDRICH ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>GIANCARLO</t>
+  </si>
+  <si>
+    <t>ANA ISABEL</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
@@ -115,7 +223,7 @@
     <t>VICTORIA VIANNEY</t>
   </si>
   <si>
-    <t>JOSE EMILIANO</t>
+    <t>NOHEMI ANGELICA</t>
   </si>
 </sst>
 </file>
@@ -539,7 +647,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -548,10 +656,10 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H3">
         <v>5.8</v>
@@ -620,10 +728,10 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -685,16 +793,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>41.67</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -705,19 +816,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>48.72</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -731,16 +845,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H4">
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -754,16 +871,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>48.65</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -777,16 +897,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>42.11</v>
+      </c>
+      <c r="H6">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -842,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>69.44</v>
+        <v>41.67</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -862,22 +985,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>48.72</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -894,16 +1017,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>82.05</v>
+        <v>56.41</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -920,16 +1043,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>72.97</v>
+        <v>48.65</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -943,16 +1066,16 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>47.37</v>
+        <v>42.11</v>
       </c>
       <c r="H6">
         <v>5.7</v>
@@ -965,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -997,22 +1120,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920237</v>
+        <v>23330051920180</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1020,22 +1143,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920330</v>
+        <v>23330051920181</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1043,22 +1166,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920270</v>
+        <v>23330051920199</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1066,22 +1189,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920276</v>
+        <v>23330051920203</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1089,24 +1212,369 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920180</v>
+        <v>23330051920254</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920327</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920247</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920310</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920363</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920345</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920319</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920300</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920302</v>
+      </c>
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920237</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920244</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920330</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920270</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920276</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920348</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920303</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="62">
   <si>
     <t>Mat</t>
   </si>
@@ -91,84 +91,72 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>CALVA</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>RUIZ</t>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DEL VALLE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
@@ -184,31 +172,22 @@
     <t>LUIS FABIAN</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
     <t>MIGUEL ENRIQUE</t>
   </si>
   <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>ANA ISABEL</t>
+  </si>
+  <si>
     <t>VANESA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>ALDRICH ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>ANA ISABEL</t>
   </si>
   <si>
     <t>LUZ YESENIA</t>
@@ -1088,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1126,10 +1105,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1149,10 +1128,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1172,10 +1151,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1195,10 +1174,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1212,16 +1191,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1235,16 +1214,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920327</v>
+        <v>23330051920254</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1258,22 +1237,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920247</v>
+        <v>23330051920310</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1281,16 +1260,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920310</v>
+        <v>23330051920363</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1304,22 +1283,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920363</v>
+        <v>23330051920302</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1327,108 +1306,108 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920345</v>
+        <v>23330051920237</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920319</v>
+        <v>23330051920244</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920300</v>
+        <v>23330051920330</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920302</v>
+        <v>23330051920270</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920237</v>
+        <v>23330051920276</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1442,22 +1421,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920244</v>
+        <v>23330051920348</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1465,116 +1444,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920330</v>
+        <v>23330051920303</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920270</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920276</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920348</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920303</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -79,15 +79,18 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BUSTOS</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>LARA</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -97,39 +100,27 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>VILLA</t>
   </si>
   <si>
     <t>DAMIAN</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -139,70 +130,43 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>MOLINA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>REGINA DAYTRI</t>
   </si>
   <si>
     <t>JESUS JAREF</t>
   </si>
   <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>ANA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
   </si>
 </sst>
 </file>
@@ -944,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>41.67</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -970,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>48.72</v>
+        <v>61.54</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -996,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>56.41</v>
+        <v>61.54</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1022,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>48.65</v>
+        <v>54.05</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1048,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>42.11</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H6">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,16 +1063,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920180</v>
+        <v>23330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1122,22 +1086,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920181</v>
+        <v>23330051920248</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1145,22 +1109,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920199</v>
+        <v>23330051920228</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1168,16 +1132,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920203</v>
+        <v>23330051920181</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1186,142 +1150,142 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920215</v>
+        <v>23330051920192</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920254</v>
+        <v>23330051920203</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920310</v>
+        <v>23330051920215</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920363</v>
+        <v>23330051920254</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920302</v>
+        <v>23330051920249</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920237</v>
+        <v>23330051920258</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1329,139 +1293,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920244</v>
+        <v>23330051920348</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920330</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920270</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920276</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920348</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920303</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -79,70 +79,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>MOLINA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
     <t>VIVIANA JOSELIN</t>
   </si>
   <si>
     <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
   </si>
   <si>
     <t>JESUS JAREF</t>
@@ -1031,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,22 +1069,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920212</v>
+        <v>23330051920248</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1086,22 +1092,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920248</v>
+        <v>23330051920228</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1109,22 +1115,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920228</v>
+        <v>23330051920308</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1132,39 +1138,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920181</v>
+        <v>23330051920311</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920192</v>
+        <v>23330051920181</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1178,16 +1184,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1201,7 +1207,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920215</v>
+        <v>23330051920203</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -1210,13 +1216,13 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1224,16 +1230,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1247,22 +1253,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920249</v>
+        <v>23330051920254</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1270,7 +1276,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920258</v>
+        <v>23330051920249</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -1279,7 +1285,7 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1293,7 +1299,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920348</v>
+        <v>23330051920258</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
@@ -1302,15 +1308,38 @@
         <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920348</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
         <v>12</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>ROSALES</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -136,13 +142,13 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>VIVIANA JOSELIN</t>
   </si>
   <si>
     <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
   </si>
   <si>
     <t>JUSTIN GIOVANNI</t>
@@ -1037,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,10 +1081,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1098,10 +1104,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1115,22 +1121,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920308</v>
+        <v>23330051920247</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1138,16 +1144,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920311</v>
+        <v>23330051920308</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1161,39 +1167,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920181</v>
+        <v>23330051920311</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920192</v>
+        <v>23330051920181</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1207,16 +1213,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1230,22 +1236,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920215</v>
+        <v>23330051920203</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1253,16 +1259,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1276,22 +1282,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920249</v>
+        <v>23330051920254</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1299,16 +1305,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920258</v>
+        <v>23330051920249</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1322,24 +1328,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920348</v>
+        <v>23330051920258</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920348</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
         <v>12</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -79,106 +79,148 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
     <t>FUENTES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>PALOMARES</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>DAMIAN</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>ROSALES</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>NURIA BELEN</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>LORENA</t>
   </si>
   <si>
     <t>VIVIANA JOSELIN</t>
   </si>
   <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
     <t>REGINA DAYTRI</t>
   </si>
   <si>
     <t>RAYMUNDO</t>
   </si>
   <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
     <t>JUSTIN GIOVANNI</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,16 +1117,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920248</v>
+        <v>23330051920254</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1098,22 +1140,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920228</v>
+        <v>23330051920239</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1121,16 +1163,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920247</v>
+        <v>23330051920241</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1144,22 +1186,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920308</v>
+        <v>23330051920245</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1167,22 +1209,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920311</v>
+        <v>23330051920267</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1190,39 +1232,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920181</v>
+        <v>23330051920319</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920192</v>
+        <v>23330051920181</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1236,16 +1278,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1259,22 +1301,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920215</v>
+        <v>23330051920203</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1282,16 +1324,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1305,22 +1347,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920249</v>
+        <v>23330051920248</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1328,22 +1370,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920258</v>
+        <v>23330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1351,24 +1393,162 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>23330051920228</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920247</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920249</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920258</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920308</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>23330051920348</v>
       </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
         <v>12</v>
       </c>
-      <c r="G14">
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920311</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -79,78 +79,69 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>ROSALES</t>
   </si>
   <si>
@@ -166,10 +157,13 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
   </si>
   <si>
     <t>MARYSOL</t>
@@ -191,15 +185,6 @@
   </si>
   <si>
     <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>VIVIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
   </si>
   <si>
     <t>REGINA DAYTRI</t>
@@ -1085,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1117,16 +1102,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1140,16 +1125,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920239</v>
+        <v>23330051920248</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1163,22 +1148,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920241</v>
+        <v>23330051920328</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1186,16 +1171,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920245</v>
+        <v>23330051920241</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1209,16 +1194,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920267</v>
+        <v>23330051920245</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1232,22 +1217,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920319</v>
+        <v>23330051920267</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1255,39 +1240,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920181</v>
+        <v>23330051920319</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920192</v>
+        <v>23330051920181</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1301,16 +1286,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1324,22 +1309,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920215</v>
+        <v>23330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1347,22 +1332,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920248</v>
+        <v>23330051920228</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1370,22 +1355,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920328</v>
+        <v>23330051920247</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1393,16 +1378,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920228</v>
+        <v>23330051920249</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1416,16 +1401,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920247</v>
+        <v>23330051920258</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1439,22 +1424,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920249</v>
+        <v>23330051920308</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1462,22 +1447,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920258</v>
+        <v>23330051920348</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1485,16 +1470,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920308</v>
+        <v>23330051920311</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1503,52 +1488,6 @@
         <v>12</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920348</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920311</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -956,7 +956,7 @@
         <v>50</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -982,7 +982,7 @@
         <v>61.54</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1008,7 +1008,7 @@
         <v>61.54</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1034,7 +1034,7 @@
         <v>54.05</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1060,7 +1060,7 @@
         <v>73.68000000000001</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -109,9 +109,6 @@
     <t>LUIS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -194,9 +188,6 @@
   </si>
   <si>
     <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
   </si>
   <si>
     <t>JUSTIN GIOVANNI</t>
@@ -947,16 +938,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>52.78</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -982,7 +973,7 @@
         <v>61.54</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -999,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>61.54</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1034,7 +1025,7 @@
         <v>54.05</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1060,7 +1051,7 @@
         <v>73.68000000000001</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1108,10 +1099,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1131,10 +1122,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1154,10 +1145,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1177,10 +1168,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1200,10 +1191,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1223,10 +1214,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1246,10 +1237,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1269,10 +1260,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1292,10 +1283,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1315,10 +1306,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1338,10 +1329,10 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1361,10 +1352,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1384,10 +1375,10 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1401,22 +1392,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920258</v>
+        <v>23330051920308</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1424,16 +1415,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920308</v>
+        <v>23330051920348</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1447,16 +1438,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920348</v>
+        <v>23330051920311</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1465,29 +1456,6 @@
         <v>12</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920311</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
         <v>1</v>
       </c>
     </row>
